--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$218</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8334" uniqueCount="834">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1662,7 +1662,7 @@
     <t>Organization.type</t>
   </si>
   <si>
-    <t>Cadre d'exercice</t>
+    <t>Kind of organization</t>
   </si>
   <si>
     <t>The kind(s) of organization that this is.</t>
@@ -1676,7 +1676,10 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS</t>
+    <t>Used to categorize the organization.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -2047,12 +2050,6 @@
     <t>Le type d’établissement détermine si c'est un établissement principal ou secondaire.</t>
   </si>
   <si>
-    <t>Used to categorize the organization.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
-  </si>
-  <si>
     <t>Organization.type:typeEtablissement.id</t>
   </si>
   <si>
@@ -2078,6 +2075,18 @@
   </si>
   <si>
     <t>Organization.type:typeEtablissement.text</t>
+  </si>
+  <si>
+    <t>Organization.type:CadreExercice</t>
+  </si>
+  <si>
+    <t>CadreExercice</t>
+  </si>
+  <si>
+    <t>Cadre d'exercice</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS</t>
   </si>
   <si>
     <t>Organization.name</t>
@@ -2909,7 +2918,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP217"/>
+  <dimension ref="A1:AP218"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -15721,7 +15730,7 @@
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>91</v>
@@ -15770,17 +15779,19 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15811,27 +15822,27 @@
         <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>529</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>78</v>
@@ -15856,7 +15867,7 @@
         <v>334</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>531</v>
@@ -15894,7 +15905,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -15933,24 +15944,24 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16065,10 +16076,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16183,13 +16194,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>546</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -16211,13 +16222,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16303,10 +16314,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16421,10 +16432,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16539,10 +16550,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16582,7 +16593,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>78</v>
@@ -16659,10 +16670,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16703,7 +16714,7 @@
         <v>78</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>78</v>
@@ -16722,7 +16733,7 @@
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>78</v>
@@ -16775,10 +16786,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16897,10 +16908,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17015,10 +17026,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17135,10 +17146,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17257,10 +17268,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17377,10 +17388,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17406,7 +17417,7 @@
         <v>176</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>430</v>
@@ -17497,10 +17508,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17617,10 +17628,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17739,10 +17750,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17861,13 +17872,13 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>529</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>78</v>
@@ -17892,7 +17903,7 @@
         <v>334</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>531</v>
@@ -17930,7 +17941,7 @@
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
@@ -17969,24 +17980,24 @@
         <v>78</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18101,10 +18112,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18221,10 +18232,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18343,10 +18354,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18461,10 +18472,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18581,10 +18592,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18703,10 +18714,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18823,10 +18834,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18852,7 +18863,7 @@
         <v>176</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M133" t="s" s="2">
         <v>430</v>
@@ -18943,10 +18954,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19063,10 +19074,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19185,10 +19196,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19307,13 +19318,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>529</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>78</v>
@@ -19338,7 +19349,7 @@
         <v>334</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M137" t="s" s="2">
         <v>531</v>
@@ -19376,7 +19387,7 @@
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>78</v>
@@ -19415,24 +19426,24 @@
         <v>78</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19547,10 +19558,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19667,10 +19678,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19789,10 +19800,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19907,10 +19918,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20027,10 +20038,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20149,10 +20160,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20269,10 +20280,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20298,7 +20309,7 @@
         <v>176</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>430</v>
@@ -20389,10 +20400,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20509,10 +20520,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20631,10 +20642,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20753,13 +20764,13 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>529</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D149" t="s" s="2">
         <v>78</v>
@@ -20784,7 +20795,7 @@
         <v>334</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M149" t="s" s="2">
         <v>531</v>
@@ -20822,7 +20833,7 @@
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>78</v>
@@ -20855,30 +20866,30 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20993,10 +21004,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21111,13 +21122,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -21139,13 +21150,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21231,10 +21242,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21349,10 +21360,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21467,10 +21478,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21510,7 +21521,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>78</v>
@@ -21587,10 +21598,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21631,7 +21642,7 @@
         <v>78</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>78</v>
@@ -21650,7 +21661,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>78</v>
@@ -21703,10 +21714,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21825,10 +21836,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21947,13 +21958,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>529</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>78</v>
@@ -21978,7 +21989,7 @@
         <v>334</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M159" t="s" s="2">
         <v>531</v>
@@ -22016,7 +22027,7 @@
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>78</v>
@@ -22049,30 +22060,30 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22187,10 +22198,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22305,13 +22316,13 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>78</v>
@@ -22333,13 +22344,13 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22425,10 +22436,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22543,10 +22554,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22661,10 +22672,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22704,7 +22715,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>78</v>
@@ -22781,10 +22792,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22825,7 +22836,7 @@
         <v>78</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>78</v>
@@ -22844,7 +22855,7 @@
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>78</v>
@@ -22897,10 +22908,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23019,10 +23030,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23141,13 +23152,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>529</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -23172,7 +23183,7 @@
         <v>334</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M169" t="s" s="2">
         <v>531</v>
@@ -23210,7 +23221,7 @@
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>78</v>
@@ -23246,27 +23257,27 @@
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23381,10 +23392,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23499,13 +23510,13 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>78</v>
@@ -23527,13 +23538,13 @@
         <v>78</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23619,10 +23630,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23737,10 +23748,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23855,10 +23866,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23898,7 +23909,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>78</v>
@@ -23975,10 +23986,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24019,7 +24030,7 @@
         <v>78</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>78</v>
@@ -24038,7 +24049,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -24091,10 +24102,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24213,10 +24224,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24335,13 +24346,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>529</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>78</v>
@@ -24366,7 +24377,7 @@
         <v>334</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M179" t="s" s="2">
         <v>531</v>
@@ -24403,10 +24414,10 @@
         <v>166</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>656</v>
+        <v>534</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>657</v>
+        <v>535</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
@@ -24445,24 +24456,24 @@
         <v>78</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24577,10 +24588,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24695,13 +24706,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24723,13 +24734,13 @@
         <v>78</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24815,10 +24826,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24933,10 +24944,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25051,10 +25062,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25094,7 +25105,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -25171,10 +25182,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25215,7 +25226,7 @@
         <v>78</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>78</v>
@@ -25234,7 +25245,7 @@
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>78</v>
@@ -25287,10 +25298,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25409,10 +25420,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25531,12 +25542,14 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C189" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="B189" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
         <v>78</v>
       </c>
@@ -25557,19 +25570,19 @@
         <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>104</v>
+        <v>334</v>
       </c>
       <c r="L189" t="s" s="2">
         <v>668</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>669</v>
+        <v>531</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>670</v>
+        <v>532</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>671</v>
+        <v>533</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>78</v>
@@ -25594,13 +25607,11 @@
         <v>78</v>
       </c>
       <c r="X189" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="Y189" s="2"/>
       <c r="Z189" t="s" s="2">
-        <v>78</v>
+        <v>669</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>78</v>
@@ -25618,45 +25629,45 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>667</v>
+        <v>529</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>672</v>
+        <v>78</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>673</v>
+        <v>78</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>674</v>
+        <v>537</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>675</v>
+        <v>538</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>676</v>
+        <v>108</v>
       </c>
       <c r="AP189" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25667,7 +25678,7 @@
         <v>79</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>91</v>
@@ -25676,22 +25687,22 @@
         <v>78</v>
       </c>
       <c r="J190" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K190" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>78</v>
@@ -25740,34 +25751,34 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="AJ190" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>78</v>
+        <v>677</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>78</v>
+        <v>679</v>
       </c>
       <c r="AP190" t="s" s="2">
         <v>78</v>
@@ -25775,10 +25786,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25801,19 +25812,19 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>685</v>
+        <v>104</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>78</v>
@@ -25850,17 +25861,19 @@
         <v>78</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AC191" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25869,25 +25882,25 @@
         <v>80</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>691</v>
+        <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>693</v>
+        <v>78</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>695</v>
+        <v>78</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>78</v>
@@ -25895,10 +25908,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25909,10 +25922,10 @@
         <v>79</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H192" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I192" t="s" s="2">
         <v>78</v>
@@ -25921,16 +25934,20 @@
         <v>78</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>104</v>
+        <v>688</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>105</v>
+        <v>689</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N192" s="2"/>
-      <c r="O192" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="P192" t="s" s="2">
         <v>78</v>
       </c>
@@ -25966,46 +25983,44 @@
         <v>78</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="AC192" s="2"/>
       <c r="AD192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>107</v>
+        <v>687</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>78</v>
+        <v>694</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>78</v>
+        <v>695</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>78</v>
+        <v>695</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>78</v>
+        <v>696</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>108</v>
+        <v>697</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>78</v>
+        <v>698</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>78</v>
@@ -26013,21 +26028,21 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>78</v>
@@ -26039,17 +26054,15 @@
         <v>78</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>78</v>
@@ -26086,31 +26099,31 @@
         <v>78</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>78</v>
@@ -26133,23 +26146,21 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C194" t="s" s="2">
-        <v>699</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>78</v>
@@ -26161,15 +26172,17 @@
         <v>78</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>700</v>
+        <v>111</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>701</v>
+        <v>112</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N194" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
         <v>78</v>
@@ -26206,16 +26219,16 @@
         <v>78</v>
       </c>
       <c r="AB194" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC194" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE194" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF194" t="s" s="2">
         <v>118</v>
@@ -26242,7 +26255,7 @@
         <v>78</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>78</v>
@@ -26253,18 +26266,20 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="C195" s="2"/>
+        <v>700</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>702</v>
+      </c>
       <c r="D195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G195" t="s" s="2">
         <v>90</v>
@@ -26276,10 +26291,10 @@
         <v>78</v>
       </c>
       <c r="J195" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>176</v>
+        <v>703</v>
       </c>
       <c r="L195" t="s" s="2">
         <v>704</v>
@@ -26312,13 +26327,13 @@
         <v>78</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>327</v>
+        <v>78</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>706</v>
+        <v>78</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>707</v>
+        <v>78</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>78</v>
@@ -26336,19 +26351,19 @@
         <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>708</v>
+        <v>118</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>709</v>
+        <v>78</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>78</v>
@@ -26357,13 +26372,13 @@
         <v>78</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>710</v>
+        <v>78</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>711</v>
+        <v>78</v>
       </c>
       <c r="AO195" t="s" s="2">
-        <v>712</v>
+        <v>78</v>
       </c>
       <c r="AP195" t="s" s="2">
         <v>78</v>
@@ -26371,10 +26386,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26397,20 +26412,16 @@
         <v>91</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>717</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="N196" s="2"/>
+      <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>78</v>
       </c>
@@ -26434,13 +26445,13 @@
         <v>78</v>
       </c>
       <c r="X196" t="s" s="2">
-        <v>78</v>
+        <v>327</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>78</v>
+        <v>709</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>78</v>
+        <v>710</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>78</v>
@@ -26458,7 +26469,7 @@
         <v>78</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -26467,7 +26478,7 @@
         <v>90</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>78</v>
+        <v>712</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>102</v>
@@ -26479,13 +26490,13 @@
         <v>78</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>365</v>
+        <v>715</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>78</v>
@@ -26493,10 +26504,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26504,7 +26515,7 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G197" t="s" s="2">
         <v>90</v>
@@ -26513,25 +26524,25 @@
         <v>78</v>
       </c>
       <c r="I197" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J197" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>176</v>
+        <v>104</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>78</v>
@@ -26556,13 +26567,13 @@
         <v>78</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>327</v>
+        <v>78</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>726</v>
+        <v>78</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>727</v>
+        <v>78</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>78</v>
@@ -26580,7 +26591,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -26601,13 +26612,13 @@
         <v>78</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>731</v>
+        <v>365</v>
       </c>
       <c r="AP197" t="s" s="2">
         <v>78</v>
@@ -26615,10 +26626,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26635,24 +26646,26 @@
         <v>78</v>
       </c>
       <c r="I198" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J198" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>733</v>
+        <v>176</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="O198" s="2"/>
+        <v>727</v>
+      </c>
+      <c r="O198" t="s" s="2">
+        <v>728</v>
+      </c>
       <c r="P198" t="s" s="2">
         <v>78</v>
       </c>
@@ -26676,13 +26689,13 @@
         <v>78</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>78</v>
+        <v>327</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>78</v>
+        <v>729</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>78</v>
+        <v>730</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>78</v>
@@ -26700,7 +26713,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26721,13 +26734,13 @@
         <v>78</v>
       </c>
       <c r="AM198" t="s" s="2">
-        <v>108</v>
+        <v>732</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>108</v>
+        <v>733</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>78</v>
+        <v>734</v>
       </c>
       <c r="AP198" t="s" s="2">
         <v>78</v>
@@ -26735,10 +26748,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26761,15 +26774,17 @@
         <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>231</v>
+        <v>736</v>
       </c>
       <c r="L199" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="M199" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="N199" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="M199" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="N199" s="2"/>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
         <v>78</v>
@@ -26818,7 +26833,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26839,13 +26854,13 @@
         <v>78</v>
       </c>
       <c r="AM199" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>742</v>
+        <v>108</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>78</v>
@@ -26853,14 +26868,12 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C200" t="s" s="2">
-        <v>744</v>
-      </c>
+        <v>741</v>
+      </c>
+      <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
         <v>78</v>
       </c>
@@ -26869,7 +26882,7 @@
         <v>79</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>78</v>
@@ -26878,23 +26891,19 @@
         <v>78</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>745</v>
+        <v>231</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>689</v>
-      </c>
+        <v>743</v>
+      </c>
+      <c r="N200" s="2"/>
+      <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>78</v>
       </c>
@@ -26942,34 +26951,34 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>684</v>
+        <v>744</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>691</v>
+        <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>747</v>
+        <v>78</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>747</v>
+        <v>78</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>693</v>
+        <v>199</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>694</v>
+        <v>745</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>695</v>
+        <v>373</v>
       </c>
       <c r="AP200" t="s" s="2">
         <v>78</v>
@@ -26977,12 +26986,14 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="C201" s="2"/>
+        <v>687</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>747</v>
+      </c>
       <c r="D201" t="s" s="2">
         <v>78</v>
       </c>
@@ -26994,7 +27005,7 @@
         <v>80</v>
       </c>
       <c r="H201" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I201" t="s" s="2">
         <v>78</v>
@@ -27003,19 +27014,19 @@
         <v>78</v>
       </c>
       <c r="K201" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="L201" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="L201" t="s" s="2">
-        <v>750</v>
-      </c>
       <c r="M201" t="s" s="2">
-        <v>751</v>
+        <v>690</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>752</v>
+        <v>691</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>753</v>
+        <v>692</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -27064,7 +27075,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>748</v>
+        <v>687</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -27076,22 +27087,22 @@
         <v>208</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>754</v>
+        <v>694</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>757</v>
+        <v>696</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>758</v>
+        <v>697</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>759</v>
+        <v>698</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>78</v>
@@ -27099,10 +27110,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27113,29 +27124,31 @@
         <v>79</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H202" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I202" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J202" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="N202" s="2"/>
+        <v>754</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="O202" t="s" s="2">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -27184,34 +27197,34 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AG202" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH202" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI202" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AJ202" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AK202" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="AL202" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AM202" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="AG202" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH202" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI202" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ202" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK202" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL202" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM202" t="s" s="2">
-        <v>525</v>
-      </c>
       <c r="AN202" t="s" s="2">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>108</v>
+        <v>762</v>
       </c>
       <c r="AP202" t="s" s="2">
         <v>78</v>
@@ -27219,10 +27232,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27242,19 +27255,21 @@
         <v>78</v>
       </c>
       <c r="J203" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>104</v>
+        <v>764</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>105</v>
+        <v>765</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>106</v>
+        <v>766</v>
       </c>
       <c r="N203" s="2"/>
-      <c r="O203" s="2"/>
+      <c r="O203" t="s" s="2">
+        <v>767</v>
+      </c>
       <c r="P203" t="s" s="2">
         <v>78</v>
       </c>
@@ -27302,7 +27317,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>107</v>
+        <v>763</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -27314,7 +27329,7 @@
         <v>78</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>78</v>
@@ -27323,13 +27338,13 @@
         <v>78</v>
       </c>
       <c r="AM203" t="s" s="2">
-        <v>78</v>
+        <v>525</v>
       </c>
       <c r="AN203" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AO203" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="AO203" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AP203" t="s" s="2">
         <v>78</v>
@@ -27337,21 +27352,21 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>78</v>
@@ -27363,17 +27378,15 @@
         <v>78</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
         <v>78</v>
@@ -27410,31 +27423,31 @@
         <v>78</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>78</v>
@@ -27457,21 +27470,21 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>78</v>
@@ -27480,19 +27493,19 @@
         <v>78</v>
       </c>
       <c r="J205" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>769</v>
+        <v>112</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>770</v>
+        <v>113</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>771</v>
+        <v>114</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27530,31 +27543,31 @@
         <v>78</v>
       </c>
       <c r="AB205" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC205" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD205" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE205" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>772</v>
+        <v>118</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>773</v>
+        <v>78</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK205" t="s" s="2">
         <v>78</v>
@@ -27566,7 +27579,7 @@
         <v>78</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>78</v>
@@ -27577,10 +27590,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27603,16 +27616,16 @@
         <v>91</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -27638,11 +27651,13 @@
         <v>78</v>
       </c>
       <c r="X206" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y206" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y206" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z206" t="s" s="2">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>78</v>
@@ -27660,7 +27675,7 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
@@ -27669,7 +27684,7 @@
         <v>90</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>78</v>
+        <v>776</v>
       </c>
       <c r="AJ206" t="s" s="2">
         <v>102</v>
@@ -27695,10 +27710,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27721,16 +27736,16 @@
         <v>91</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>301</v>
+        <v>137</v>
       </c>
       <c r="L207" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="M207" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="N207" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="M207" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -27756,13 +27771,11 @@
         <v>78</v>
       </c>
       <c r="X207" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y207" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y207" s="2"/>
       <c r="Z207" t="s" s="2">
-        <v>78</v>
+        <v>543</v>
       </c>
       <c r="AA207" t="s" s="2">
         <v>78</v>
@@ -27780,7 +27793,7 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27804,7 +27817,7 @@
         <v>78</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>784</v>
+        <v>199</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>78</v>
@@ -27815,10 +27828,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27841,16 +27854,16 @@
         <v>91</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>104</v>
+        <v>301</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -27900,7 +27913,7 @@
         <v>78</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27924,7 +27937,7 @@
         <v>78</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>199</v>
+        <v>787</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>78</v>
@@ -27935,10 +27948,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27949,7 +27962,7 @@
         <v>79</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>78</v>
@@ -27958,23 +27971,21 @@
         <v>78</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K209" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L209" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="M209" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="N209" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="L209" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="M209" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>795</v>
-      </c>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>78</v>
       </c>
@@ -28022,13 +28033,13 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>78</v>
@@ -28046,7 +28057,7 @@
         <v>78</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>796</v>
+        <v>199</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>78</v>
@@ -28057,10 +28068,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28071,7 +28082,7 @@
         <v>79</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>78</v>
@@ -28083,16 +28094,20 @@
         <v>78</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>104</v>
+        <v>794</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>105</v>
+        <v>795</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N210" s="2"/>
-      <c r="O210" s="2"/>
+        <v>796</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="O210" t="s" s="2">
+        <v>798</v>
+      </c>
       <c r="P210" t="s" s="2">
         <v>78</v>
       </c>
@@ -28140,19 +28155,19 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>107</v>
+        <v>793</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>78</v>
@@ -28164,7 +28179,7 @@
         <v>78</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>108</v>
+        <v>799</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>78</v>
@@ -28175,21 +28190,21 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>78</v>
@@ -28201,17 +28216,15 @@
         <v>78</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N211" s="2"/>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>78</v>
@@ -28260,19 +28273,19 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>78</v>
@@ -28295,14 +28308,14 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>800</v>
+        <v>110</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -28315,26 +28328,24 @@
         <v>78</v>
       </c>
       <c r="I212" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K212" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>801</v>
+        <v>112</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>802</v>
+        <v>113</v>
       </c>
       <c r="N212" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O212" t="s" s="2">
-        <v>298</v>
-      </c>
+      <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>78</v>
       </c>
@@ -28382,7 +28393,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>803</v>
+        <v>118</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28406,7 +28417,7 @@
         <v>78</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>78</v>
@@ -28417,43 +28428,45 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
-        <v>78</v>
+        <v>803</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I213" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>334</v>
+        <v>111</v>
       </c>
       <c r="L213" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="M213" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="M213" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="N213" s="2"/>
+      <c r="N213" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O213" t="s" s="2">
-        <v>807</v>
+        <v>298</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>78</v>
@@ -28478,13 +28491,13 @@
         <v>78</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>808</v>
+        <v>78</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>809</v>
+        <v>78</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
@@ -28502,19 +28515,19 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>78</v>
@@ -28526,7 +28539,7 @@
         <v>78</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>810</v>
+        <v>199</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>78</v>
@@ -28537,10 +28550,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28563,17 +28576,17 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>812</v>
+        <v>334</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" t="s" s="2">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28598,13 +28611,13 @@
         <v>78</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>78</v>
+        <v>811</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>78</v>
+        <v>812</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>78</v>
@@ -28622,7 +28635,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28643,10 +28656,10 @@
         <v>78</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>816</v>
+        <v>78</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28657,10 +28670,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28671,7 +28684,7 @@
         <v>79</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>78</v>
@@ -28683,17 +28696,17 @@
         <v>78</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>685</v>
+        <v>815</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>687</v>
+        <v>817</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28742,19 +28755,19 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI215" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>821</v>
+        <v>102</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>78</v>
@@ -28763,13 +28776,13 @@
         <v>78</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>693</v>
+        <v>819</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>694</v>
+        <v>820</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>695</v>
+        <v>78</v>
       </c>
       <c r="AP215" t="s" s="2">
         <v>78</v>
@@ -28777,10 +28790,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28791,7 +28804,7 @@
         <v>79</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>78</v>
@@ -28803,19 +28816,17 @@
         <v>78</v>
       </c>
       <c r="K216" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="L216" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="M216" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="N216" s="2"/>
+      <c r="O216" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="L216" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="M216" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="N216" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>825</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28864,19 +28875,19 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI216" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>102</v>
+        <v>824</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>78</v>
@@ -28885,13 +28896,13 @@
         <v>78</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>757</v>
+        <v>696</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>758</v>
+        <v>697</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>759</v>
+        <v>698</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>78</v>
@@ -28899,10 +28910,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28913,10 +28924,10 @@
         <v>79</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>78</v>
@@ -28925,17 +28936,19 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="L217" t="s" s="2">
         <v>827</v>
       </c>
-      <c r="L217" t="s" s="2">
+      <c r="M217" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="N217" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="O217" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="M217" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="N217" s="2"/>
-      <c r="O217" t="s" s="2">
-        <v>830</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28984,16 +28997,16 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH217" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ217" t="s" s="2">
         <v>102</v>
@@ -29005,20 +29018,140 @@
         <v>78</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>78</v>
+        <v>760</v>
       </c>
       <c r="AN217" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AO217" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="AP217" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="218" hidden="true">
+      <c r="A218" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="C218" s="2"/>
+      <c r="D218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G218" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H218" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K218" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="L218" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="N218" s="2"/>
+      <c r="O218" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="P218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q218" s="2"/>
+      <c r="R218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF218" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="AG218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH218" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ218" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN218" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AO217" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP217" t="s" s="2">
+      <c r="AO218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP218" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP217">
+  <autoFilter ref="A1:AP218">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -29028,7 +29161,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI216">
+  <conditionalFormatting sqref="A2:AI217">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$273</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8441" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10387" uniqueCount="940">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2421,6 +2421,255 @@
   </si>
   <si>
     <t>EntiteJuridique.boiteLettreMSS</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t>as-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
+</t>
+  </si>
+  <si>
+    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
+  </si>
+  <si>
+    <t>Extension contenant les métadonnées de la mailbox mss.</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>typeBAL : Type de boîte aux lettres.
+Valeurs possibles : ORG | APP | PER | CAB</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible</t>
+  </si>
+  <si>
+    <t>responsible</t>
+  </si>
+  <si>
+    <t>responsable : Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>telephone : Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté.</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization</t>
+  </si>
+  <si>
+    <t>digitization</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge</t>
+  </si>
+  <si>
+    <t>listeRouge</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.system</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.value</t>
+  </si>
+  <si>
+    <t>Boîte Aux Lettres (BAL) MSS</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.use</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.rank</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -3004,11 +3253,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP221"/>
+  <dimension ref="A1:AP273"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.52734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="97.4375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.4375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="40.16796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -3017,7 +3266,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="145.890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -27545,7 +27794,7 @@
         <v>775</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>775</v>
+        <v>723</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27556,10 +27805,10 @@
         <v>80</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>79</v>
@@ -27568,20 +27817,16 @@
         <v>79</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>776</v>
+        <v>105</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>777</v>
+        <v>106</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="N205" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>780</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N205" s="2"/>
+      <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
         <v>79</v>
       </c>
@@ -27629,34 +27874,34 @@
         <v>79</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>775</v>
+        <v>108</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>781</v>
+        <v>79</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>782</v>
+        <v>79</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>783</v>
+        <v>79</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>784</v>
+        <v>79</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>785</v>
+        <v>109</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>786</v>
+        <v>79</v>
       </c>
       <c r="AP205" t="s" s="2">
         <v>79</v>
@@ -27664,10 +27909,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>787</v>
+        <v>724</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27675,10 +27920,10 @@
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>79</v>
@@ -27687,21 +27932,19 @@
         <v>79</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>788</v>
+        <v>112</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>789</v>
+        <v>202</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>790</v>
+        <v>203</v>
       </c>
       <c r="N206" s="2"/>
-      <c r="O206" t="s" s="2">
-        <v>791</v>
-      </c>
+      <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>79</v>
       </c>
@@ -27737,46 +27980,46 @@
         <v>79</v>
       </c>
       <c r="AB206" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC206" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE206" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>787</v>
+        <v>119</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>792</v>
+        <v>79</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>536</v>
+        <v>79</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>793</v>
+        <v>79</v>
       </c>
       <c r="AO206" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AP206" t="s" s="2">
         <v>79</v>
@@ -27784,18 +28027,20 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>794</v>
+        <v>777</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="C207" s="2"/>
+        <v>724</v>
+      </c>
+      <c r="C207" t="s" s="2">
+        <v>726</v>
+      </c>
       <c r="D207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G207" t="s" s="2">
         <v>91</v>
@@ -27810,13 +28055,13 @@
         <v>79</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>105</v>
+        <v>727</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>106</v>
+        <v>728</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>107</v>
+        <v>729</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -27867,19 +28112,19 @@
         <v>79</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>79</v>
@@ -27891,7 +28136,7 @@
         <v>79</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>79</v>
@@ -27902,21 +28147,21 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H208" t="s" s="2">
         <v>79</v>
@@ -27928,17 +28173,15 @@
         <v>79</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>79</v>
@@ -27975,31 +28218,31 @@
         <v>79</v>
       </c>
       <c r="AB208" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC208" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD208" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE208" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI208" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>79</v>
@@ -28022,10 +28265,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28036,7 +28279,7 @@
         <v>80</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>79</v>
@@ -28045,20 +28288,18 @@
         <v>79</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>797</v>
+        <v>202</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>799</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N209" s="2"/>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>79</v>
@@ -28095,31 +28336,31 @@
         <v>79</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>800</v>
+        <v>119</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI209" t="s" s="2">
-        <v>801</v>
+        <v>79</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>79</v>
@@ -28131,7 +28372,7 @@
         <v>79</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>79</v>
@@ -28142,10 +28383,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>802</v>
+        <v>782</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>802</v>
+        <v>783</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28153,7 +28394,7 @@
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G210" t="s" s="2">
         <v>91</v>
@@ -28165,19 +28406,19 @@
         <v>79</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K210" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>803</v>
+        <v>224</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>804</v>
+        <v>225</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>805</v>
+        <v>226</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -28185,7 +28426,7 @@
       </c>
       <c r="Q210" s="2"/>
       <c r="R210" t="s" s="2">
-        <v>79</v>
+        <v>784</v>
       </c>
       <c r="S210" t="s" s="2">
         <v>79</v>
@@ -28203,11 +28444,13 @@
         <v>79</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y210" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y210" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z210" t="s" s="2">
-        <v>554</v>
+        <v>79</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>79</v>
@@ -28225,10 +28468,10 @@
         <v>79</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>806</v>
+        <v>228</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>91</v>
@@ -28237,7 +28480,7 @@
         <v>79</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>79</v>
@@ -28260,10 +28503,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>807</v>
+        <v>785</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>807</v>
+        <v>786</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28283,20 +28526,18 @@
         <v>79</v>
       </c>
       <c r="J211" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>305</v>
+        <v>155</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>808</v>
+        <v>232</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>810</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="N211" s="2"/>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>79</v>
@@ -28306,7 +28547,7 @@
         <v>79</v>
       </c>
       <c r="S211" t="s" s="2">
-        <v>79</v>
+        <v>787</v>
       </c>
       <c r="T211" t="s" s="2">
         <v>79</v>
@@ -28321,13 +28562,11 @@
         <v>79</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y211" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>79</v>
+        <v>788</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>79</v>
@@ -28345,7 +28584,7 @@
         <v>79</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>811</v>
+        <v>234</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -28369,7 +28608,7 @@
         <v>79</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>812</v>
+        <v>200</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>79</v>
@@ -28380,12 +28619,14 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>813</v>
+        <v>789</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="C212" s="2"/>
+        <v>724</v>
+      </c>
+      <c r="C212" t="s" s="2">
+        <v>790</v>
+      </c>
       <c r="D212" t="s" s="2">
         <v>79</v>
       </c>
@@ -28403,20 +28644,18 @@
         <v>79</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>105</v>
+        <v>791</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>814</v>
+        <v>792</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>816</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="N212" s="2"/>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>79</v>
@@ -28465,19 +28704,19 @@
         <v>79</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>817</v>
+        <v>119</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>79</v>
@@ -28489,7 +28728,7 @@
         <v>79</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>79</v>
@@ -28500,10 +28739,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>818</v>
+        <v>794</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>818</v>
+        <v>779</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28514,7 +28753,7 @@
         <v>80</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>79</v>
@@ -28526,20 +28765,16 @@
         <v>79</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>819</v>
+        <v>105</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>820</v>
+        <v>106</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="N213" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="O213" t="s" s="2">
-        <v>823</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N213" s="2"/>
+      <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>79</v>
       </c>
@@ -28587,19 +28822,19 @@
         <v>79</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>818</v>
+        <v>108</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>79</v>
@@ -28611,7 +28846,7 @@
         <v>79</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>824</v>
+        <v>109</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>79</v>
@@ -28622,21 +28857,21 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>825</v>
+        <v>795</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>825</v>
+        <v>781</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>79</v>
@@ -28648,15 +28883,17 @@
         <v>79</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N214" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>79</v>
@@ -28693,31 +28930,31 @@
         <v>79</v>
       </c>
       <c r="AB214" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC214" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE214" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>79</v>
@@ -28740,21 +28977,23 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>826</v>
+        <v>796</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="C215" s="2"/>
+        <v>781</v>
+      </c>
+      <c r="C215" t="s" s="2">
+        <v>797</v>
+      </c>
       <c r="D215" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>79</v>
@@ -28769,14 +29008,12 @@
         <v>112</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>113</v>
+        <v>798</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>79</v>
@@ -28849,7 +29086,7 @@
         <v>79</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>79</v>
@@ -28860,46 +29097,42 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>827</v>
+        <v>799</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>827</v>
+        <v>800</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>828</v>
+        <v>79</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I216" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>829</v>
+        <v>106</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="N216" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N216" s="2"/>
+      <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
         <v>79</v>
       </c>
@@ -28947,19 +29180,19 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>831</v>
+        <v>108</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>79</v>
@@ -28971,7 +29204,7 @@
         <v>79</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>79</v>
@@ -28982,10 +29215,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>832</v>
+        <v>801</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>832</v>
+        <v>802</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28996,7 +29229,7 @@
         <v>80</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H217" t="s" s="2">
         <v>79</v>
@@ -29008,18 +29241,16 @@
         <v>79</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>339</v>
+        <v>112</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>833</v>
+        <v>202</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>834</v>
+        <v>203</v>
       </c>
       <c r="N217" s="2"/>
-      <c r="O217" t="s" s="2">
-        <v>835</v>
-      </c>
+      <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
         <v>79</v>
       </c>
@@ -29043,43 +29274,43 @@
         <v>79</v>
       </c>
       <c r="X217" t="s" s="2">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>836</v>
+        <v>79</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>837</v>
+        <v>79</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB217" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC217" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD217" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE217" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>832</v>
+        <v>119</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH217" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI217" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>79</v>
@@ -29091,7 +29322,7 @@
         <v>79</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>838</v>
+        <v>79</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>79</v>
@@ -29102,10 +29333,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>839</v>
+        <v>803</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>839</v>
+        <v>804</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29113,7 +29344,7 @@
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G218" t="s" s="2">
         <v>91</v>
@@ -29128,24 +29359,24 @@
         <v>79</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>840</v>
+        <v>138</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>841</v>
+        <v>224</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="N218" s="2"/>
-      <c r="O218" t="s" s="2">
-        <v>843</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N218" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q218" s="2"/>
       <c r="R218" t="s" s="2">
-        <v>79</v>
+        <v>797</v>
       </c>
       <c r="S218" t="s" s="2">
         <v>79</v>
@@ -29187,10 +29418,10 @@
         <v>79</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>839</v>
+        <v>228</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>91</v>
@@ -29199,7 +29430,7 @@
         <v>79</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK218" t="s" s="2">
         <v>79</v>
@@ -29208,10 +29439,10 @@
         <v>79</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>844</v>
+        <v>79</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>845</v>
+        <v>200</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>79</v>
@@ -29222,10 +29453,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>846</v>
+        <v>805</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>846</v>
+        <v>806</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29236,7 +29467,7 @@
         <v>80</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>79</v>
@@ -29248,18 +29479,16 @@
         <v>79</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>711</v>
+        <v>339</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>847</v>
+        <v>232</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>713</v>
+        <v>573</v>
       </c>
       <c r="N219" s="2"/>
-      <c r="O219" t="s" s="2">
-        <v>848</v>
-      </c>
+      <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
         <v>79</v>
       </c>
@@ -29283,13 +29512,11 @@
         <v>79</v>
       </c>
       <c r="X219" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y219" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="Y219" s="2"/>
       <c r="Z219" t="s" s="2">
-        <v>79</v>
+        <v>807</v>
       </c>
       <c r="AA219" t="s" s="2">
         <v>79</v>
@@ -29307,19 +29534,19 @@
         <v>79</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>846</v>
+        <v>234</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>849</v>
+        <v>103</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>79</v>
@@ -29328,13 +29555,13 @@
         <v>79</v>
       </c>
       <c r="AM219" t="s" s="2">
-        <v>720</v>
+        <v>79</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>721</v>
+        <v>200</v>
       </c>
       <c r="AO219" t="s" s="2">
-        <v>722</v>
+        <v>79</v>
       </c>
       <c r="AP219" t="s" s="2">
         <v>79</v>
@@ -29342,12 +29569,14 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>850</v>
+        <v>808</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="C220" s="2"/>
+        <v>781</v>
+      </c>
+      <c r="C220" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="D220" t="s" s="2">
         <v>79</v>
       </c>
@@ -29368,20 +29597,16 @@
         <v>79</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>851</v>
+        <v>112</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>852</v>
+        <v>202</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="N220" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="O220" t="s" s="2">
-        <v>853</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
         <v>79</v>
       </c>
@@ -29429,19 +29654,19 @@
         <v>79</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>850</v>
+        <v>119</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK220" t="s" s="2">
         <v>79</v>
@@ -29450,13 +29675,13 @@
         <v>79</v>
       </c>
       <c r="AM220" t="s" s="2">
-        <v>784</v>
+        <v>79</v>
       </c>
       <c r="AN220" t="s" s="2">
-        <v>785</v>
+        <v>79</v>
       </c>
       <c r="AO220" t="s" s="2">
-        <v>786</v>
+        <v>79</v>
       </c>
       <c r="AP220" t="s" s="2">
         <v>79</v>
@@ -29464,10 +29689,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>854</v>
+        <v>809</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>854</v>
+        <v>800</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29478,10 +29703,10 @@
         <v>80</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>79</v>
@@ -29490,18 +29715,16 @@
         <v>79</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>855</v>
+        <v>105</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>856</v>
+        <v>106</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>857</v>
+        <v>107</v>
       </c>
       <c r="N221" s="2"/>
-      <c r="O221" t="s" s="2">
-        <v>858</v>
-      </c>
+      <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
         <v>79</v>
       </c>
@@ -29549,19 +29772,19 @@
         <v>79</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>854</v>
+        <v>108</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI221" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>79</v>
@@ -29582,8 +29805,6214 @@
         <v>79</v>
       </c>
     </row>
+    <row r="222" hidden="true">
+      <c r="A222" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C222" s="2"/>
+      <c r="D222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E222" s="2"/>
+      <c r="F222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K222" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L222" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M222" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N222" s="2"/>
+      <c r="O222" s="2"/>
+      <c r="P222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q222" s="2"/>
+      <c r="R222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB222" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC222" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE222" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF222" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH222" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ222" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP222" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="223" hidden="true">
+      <c r="A223" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C223" s="2"/>
+      <c r="D223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G223" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K223" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L223" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M223" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N223" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O223" s="2"/>
+      <c r="P223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q223" s="2"/>
+      <c r="R223" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="S223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF223" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG223" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH223" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN223" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP223" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="224" hidden="true">
+      <c r="A224" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="C224" s="2"/>
+      <c r="D224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E224" s="2"/>
+      <c r="F224" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G224" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K224" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L224" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M224" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N224" s="2"/>
+      <c r="O224" s="2"/>
+      <c r="P224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q224" s="2"/>
+      <c r="R224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF224" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG224" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH224" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ224" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN224" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO224" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP224" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="225" hidden="true">
+      <c r="A225" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C225" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="D225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E225" s="2"/>
+      <c r="F225" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G225" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K225" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L225" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="M225" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N225" s="2"/>
+      <c r="O225" s="2"/>
+      <c r="P225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q225" s="2"/>
+      <c r="R225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF225" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG225" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH225" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ225" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO225" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP225" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="226" hidden="true">
+      <c r="A226" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="C226" s="2"/>
+      <c r="D226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E226" s="2"/>
+      <c r="F226" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G226" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K226" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L226" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M226" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N226" s="2"/>
+      <c r="O226" s="2"/>
+      <c r="P226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q226" s="2"/>
+      <c r="R226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF226" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG226" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH226" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN226" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO226" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP226" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="227" hidden="true">
+      <c r="A227" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C227" s="2"/>
+      <c r="D227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E227" s="2"/>
+      <c r="F227" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G227" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K227" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L227" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M227" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N227" s="2"/>
+      <c r="O227" s="2"/>
+      <c r="P227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q227" s="2"/>
+      <c r="R227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB227" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC227" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE227" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF227" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG227" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH227" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ227" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO227" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP227" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="228" hidden="true">
+      <c r="A228" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C228" s="2"/>
+      <c r="D228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E228" s="2"/>
+      <c r="F228" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G228" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K228" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L228" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M228" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N228" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O228" s="2"/>
+      <c r="P228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q228" s="2"/>
+      <c r="R228" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="S228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF228" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG228" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH228" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN228" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO228" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP228" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="229" hidden="true">
+      <c r="A229" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="C229" s="2"/>
+      <c r="D229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E229" s="2"/>
+      <c r="F229" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G229" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K229" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L229" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M229" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N229" s="2"/>
+      <c r="O229" s="2"/>
+      <c r="P229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q229" s="2"/>
+      <c r="R229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF229" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG229" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH229" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ229" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN229" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO229" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP229" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="230" hidden="true">
+      <c r="A230" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C230" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="D230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E230" s="2"/>
+      <c r="F230" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G230" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K230" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L230" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M230" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N230" s="2"/>
+      <c r="O230" s="2"/>
+      <c r="P230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q230" s="2"/>
+      <c r="R230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF230" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG230" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH230" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ230" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP230" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="231" hidden="true">
+      <c r="A231" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="C231" s="2"/>
+      <c r="D231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E231" s="2"/>
+      <c r="F231" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G231" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K231" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L231" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M231" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N231" s="2"/>
+      <c r="O231" s="2"/>
+      <c r="P231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q231" s="2"/>
+      <c r="R231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF231" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG231" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH231" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN231" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP231" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="232" hidden="true">
+      <c r="A232" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C232" s="2"/>
+      <c r="D232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E232" s="2"/>
+      <c r="F232" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G232" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K232" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L232" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M232" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N232" s="2"/>
+      <c r="O232" s="2"/>
+      <c r="P232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q232" s="2"/>
+      <c r="R232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB232" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC232" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE232" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF232" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG232" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH232" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ232" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP232" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="233" hidden="true">
+      <c r="A233" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C233" s="2"/>
+      <c r="D233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E233" s="2"/>
+      <c r="F233" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G233" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K233" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L233" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M233" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N233" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O233" s="2"/>
+      <c r="P233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q233" s="2"/>
+      <c r="R233" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="S233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF233" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG233" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH233" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN233" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP233" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="234" hidden="true">
+      <c r="A234" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="C234" s="2"/>
+      <c r="D234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E234" s="2"/>
+      <c r="F234" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G234" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K234" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L234" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M234" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N234" s="2"/>
+      <c r="O234" s="2"/>
+      <c r="P234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q234" s="2"/>
+      <c r="R234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF234" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG234" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH234" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ234" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN234" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO234" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP234" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="235" hidden="true">
+      <c r="A235" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C235" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="D235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E235" s="2"/>
+      <c r="F235" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G235" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K235" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L235" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="M235" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N235" s="2"/>
+      <c r="O235" s="2"/>
+      <c r="P235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q235" s="2"/>
+      <c r="R235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF235" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG235" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH235" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ235" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO235" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP235" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="236" hidden="true">
+      <c r="A236" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="C236" s="2"/>
+      <c r="D236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E236" s="2"/>
+      <c r="F236" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G236" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K236" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L236" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M236" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N236" s="2"/>
+      <c r="O236" s="2"/>
+      <c r="P236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q236" s="2"/>
+      <c r="R236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF236" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG236" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH236" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN236" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO236" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP236" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="237" hidden="true">
+      <c r="A237" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C237" s="2"/>
+      <c r="D237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E237" s="2"/>
+      <c r="F237" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G237" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K237" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L237" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M237" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N237" s="2"/>
+      <c r="O237" s="2"/>
+      <c r="P237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q237" s="2"/>
+      <c r="R237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB237" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC237" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE237" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF237" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG237" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH237" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ237" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO237" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP237" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="238" hidden="true">
+      <c r="A238" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C238" s="2"/>
+      <c r="D238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E238" s="2"/>
+      <c r="F238" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G238" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K238" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L238" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M238" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N238" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O238" s="2"/>
+      <c r="P238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q238" s="2"/>
+      <c r="R238" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="S238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF238" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG238" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH238" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN238" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO238" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP238" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="239" hidden="true">
+      <c r="A239" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="C239" s="2"/>
+      <c r="D239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E239" s="2"/>
+      <c r="F239" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G239" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K239" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L239" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M239" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N239" s="2"/>
+      <c r="O239" s="2"/>
+      <c r="P239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q239" s="2"/>
+      <c r="R239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF239" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG239" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH239" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ239" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN239" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP239" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="240" hidden="true">
+      <c r="A240" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C240" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="D240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E240" s="2"/>
+      <c r="F240" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G240" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K240" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L240" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M240" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N240" s="2"/>
+      <c r="O240" s="2"/>
+      <c r="P240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q240" s="2"/>
+      <c r="R240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF240" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG240" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH240" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ240" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO240" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP240" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="241" hidden="true">
+      <c r="A241" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="C241" s="2"/>
+      <c r="D241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E241" s="2"/>
+      <c r="F241" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G241" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K241" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L241" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M241" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N241" s="2"/>
+      <c r="O241" s="2"/>
+      <c r="P241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q241" s="2"/>
+      <c r="R241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF241" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG241" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH241" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN241" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO241" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP241" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="242" hidden="true">
+      <c r="A242" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C242" s="2"/>
+      <c r="D242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E242" s="2"/>
+      <c r="F242" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G242" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K242" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L242" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M242" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N242" s="2"/>
+      <c r="O242" s="2"/>
+      <c r="P242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q242" s="2"/>
+      <c r="R242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB242" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC242" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE242" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF242" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG242" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH242" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ242" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO242" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP242" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="243" hidden="true">
+      <c r="A243" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C243" s="2"/>
+      <c r="D243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E243" s="2"/>
+      <c r="F243" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G243" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K243" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L243" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M243" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N243" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O243" s="2"/>
+      <c r="P243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q243" s="2"/>
+      <c r="R243" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="S243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF243" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG243" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH243" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN243" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO243" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP243" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="244" hidden="true">
+      <c r="A244" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="C244" s="2"/>
+      <c r="D244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E244" s="2"/>
+      <c r="F244" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G244" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K244" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L244" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M244" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N244" s="2"/>
+      <c r="O244" s="2"/>
+      <c r="P244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q244" s="2"/>
+      <c r="R244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF244" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG244" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH244" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ244" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN244" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO244" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP244" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="245" hidden="true">
+      <c r="A245" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C245" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="D245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E245" s="2"/>
+      <c r="F245" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G245" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K245" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L245" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M245" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N245" s="2"/>
+      <c r="O245" s="2"/>
+      <c r="P245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q245" s="2"/>
+      <c r="R245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF245" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG245" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH245" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ245" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO245" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP245" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="246" hidden="true">
+      <c r="A246" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="C246" s="2"/>
+      <c r="D246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E246" s="2"/>
+      <c r="F246" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G246" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K246" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L246" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M246" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N246" s="2"/>
+      <c r="O246" s="2"/>
+      <c r="P246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q246" s="2"/>
+      <c r="R246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF246" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG246" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH246" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN246" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO246" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP246" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="247" hidden="true">
+      <c r="A247" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E247" s="2"/>
+      <c r="F247" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G247" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K247" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L247" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M247" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N247" s="2"/>
+      <c r="O247" s="2"/>
+      <c r="P247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q247" s="2"/>
+      <c r="R247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB247" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC247" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE247" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF247" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG247" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH247" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ247" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO247" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP247" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="248" hidden="true">
+      <c r="A248" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C248" s="2"/>
+      <c r="D248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E248" s="2"/>
+      <c r="F248" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G248" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K248" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L248" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M248" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N248" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O248" s="2"/>
+      <c r="P248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q248" s="2"/>
+      <c r="R248" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="S248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF248" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG248" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH248" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN248" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO248" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP248" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="249" hidden="true">
+      <c r="A249" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="C249" s="2"/>
+      <c r="D249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E249" s="2"/>
+      <c r="F249" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G249" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K249" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L249" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M249" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N249" s="2"/>
+      <c r="O249" s="2"/>
+      <c r="P249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q249" s="2"/>
+      <c r="R249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF249" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG249" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH249" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ249" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN249" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO249" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP249" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="250" hidden="true">
+      <c r="A250" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="C250" s="2"/>
+      <c r="D250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E250" s="2"/>
+      <c r="F250" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G250" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K250" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L250" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M250" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N250" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O250" s="2"/>
+      <c r="P250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q250" s="2"/>
+      <c r="R250" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="S250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF250" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG250" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH250" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN250" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO250" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP250" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="251" hidden="true">
+      <c r="A251" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="C251" s="2"/>
+      <c r="D251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E251" s="2"/>
+      <c r="F251" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G251" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K251" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="L251" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M251" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N251" s="2"/>
+      <c r="O251" s="2"/>
+      <c r="P251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q251" s="2"/>
+      <c r="R251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF251" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG251" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH251" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ251" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN251" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO251" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP251" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="252" hidden="true">
+      <c r="A252" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C252" s="2"/>
+      <c r="D252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E252" s="2"/>
+      <c r="F252" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G252" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J252" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K252" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L252" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="M252" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N252" s="2"/>
+      <c r="O252" s="2"/>
+      <c r="P252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q252" s="2"/>
+      <c r="R252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S252" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="T252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X252" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Y252" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="Z252" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AA252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF252" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AG252" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH252" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI252" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AJ252" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL252" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM252" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AN252" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="AO252" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="AP252" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="253" hidden="true">
+      <c r="A253" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C253" s="2"/>
+      <c r="D253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E253" s="2"/>
+      <c r="F253" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G253" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H253" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J253" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K253" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L253" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="M253" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="N253" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="O253" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="P253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q253" s="2"/>
+      <c r="R253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF253" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="AG253" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH253" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ253" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL253" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM253" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="AN253" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="AO253" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AP253" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="254" hidden="true">
+      <c r="A254" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="C254" s="2"/>
+      <c r="D254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E254" s="2"/>
+      <c r="F254" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G254" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I254" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J254" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K254" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L254" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="M254" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="N254" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="O254" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="P254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q254" s="2"/>
+      <c r="R254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X254" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Y254" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="Z254" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AA254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF254" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AG254" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH254" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ254" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL254" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM254" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AN254" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AO254" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="AP254" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="255" hidden="true">
+      <c r="A255" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C255" s="2"/>
+      <c r="D255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E255" s="2"/>
+      <c r="F255" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G255" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J255" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K255" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="L255" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M255" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="N255" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="O255" s="2"/>
+      <c r="P255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q255" s="2"/>
+      <c r="R255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF255" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AG255" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH255" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ255" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM255" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AN255" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO255" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP255" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="256" hidden="true">
+      <c r="A256" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="C256" s="2"/>
+      <c r="D256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E256" s="2"/>
+      <c r="F256" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G256" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J256" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K256" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L256" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="M256" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="N256" s="2"/>
+      <c r="O256" s="2"/>
+      <c r="P256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q256" s="2"/>
+      <c r="R256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF256" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AG256" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH256" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ256" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL256" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM256" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AN256" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AO256" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP256" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="257" hidden="true">
+      <c r="A257" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="C257" s="2"/>
+      <c r="D257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E257" s="2"/>
+      <c r="F257" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G257" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H257" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K257" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="L257" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="M257" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="N257" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="O257" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="P257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q257" s="2"/>
+      <c r="R257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE257" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF257" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="AG257" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH257" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI257" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AJ257" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="AK257" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="AL257" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="AM257" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="AN257" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="AO257" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="AP257" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="258" hidden="true">
+      <c r="A258" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="C258" s="2"/>
+      <c r="D258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E258" s="2"/>
+      <c r="F258" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G258" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J258" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K258" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="L258" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="M258" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="N258" s="2"/>
+      <c r="O258" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="P258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q258" s="2"/>
+      <c r="R258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF258" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AG258" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH258" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ258" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK258" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL258" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="AM258" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN258" t="s" s="2">
+        <v>874</v>
+      </c>
+      <c r="AO258" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AP258" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="259" hidden="true">
+      <c r="A259" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="C259" s="2"/>
+      <c r="D259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E259" s="2"/>
+      <c r="F259" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G259" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K259" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L259" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M259" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N259" s="2"/>
+      <c r="O259" s="2"/>
+      <c r="P259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q259" s="2"/>
+      <c r="R259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF259" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG259" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH259" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN259" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO259" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP259" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="260" hidden="true">
+      <c r="A260" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="C260" s="2"/>
+      <c r="D260" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E260" s="2"/>
+      <c r="F260" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G260" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K260" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L260" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M260" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N260" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O260" s="2"/>
+      <c r="P260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q260" s="2"/>
+      <c r="R260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB260" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC260" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE260" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF260" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG260" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH260" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ260" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN260" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO260" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP260" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="261" hidden="true">
+      <c r="A261" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="C261" s="2"/>
+      <c r="D261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E261" s="2"/>
+      <c r="F261" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G261" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J261" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K261" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L261" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="M261" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="N261" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="O261" s="2"/>
+      <c r="P261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q261" s="2"/>
+      <c r="R261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF261" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="AG261" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH261" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI261" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="AJ261" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN261" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO261" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP261" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="262" hidden="true">
+      <c r="A262" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="C262" s="2"/>
+      <c r="D262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E262" s="2"/>
+      <c r="F262" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G262" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J262" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K262" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L262" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="M262" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="N262" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="O262" s="2"/>
+      <c r="P262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q262" s="2"/>
+      <c r="R262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X262" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y262" s="2"/>
+      <c r="Z262" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AA262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF262" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="AG262" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH262" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ262" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN262" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO262" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP262" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="263" hidden="true">
+      <c r="A263" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="C263" s="2"/>
+      <c r="D263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E263" s="2"/>
+      <c r="F263" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G263" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J263" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K263" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L263" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="M263" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="N263" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="O263" s="2"/>
+      <c r="P263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q263" s="2"/>
+      <c r="R263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF263" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="AG263" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH263" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ263" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN263" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="AO263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP263" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="264" hidden="true">
+      <c r="A264" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="C264" s="2"/>
+      <c r="D264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E264" s="2"/>
+      <c r="F264" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G264" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J264" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K264" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L264" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="M264" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="N264" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="O264" s="2"/>
+      <c r="P264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q264" s="2"/>
+      <c r="R264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF264" t="s" s="2">
+        <v>898</v>
+      </c>
+      <c r="AG264" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH264" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ264" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN264" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO264" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP264" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="265" hidden="true">
+      <c r="A265" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="C265" s="2"/>
+      <c r="D265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E265" s="2"/>
+      <c r="F265" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G265" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K265" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="L265" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="M265" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="N265" t="s" s="2">
+        <v>903</v>
+      </c>
+      <c r="O265" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="P265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q265" s="2"/>
+      <c r="R265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF265" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="AG265" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH265" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ265" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN265" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="AO265" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP265" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="266" hidden="true">
+      <c r="A266" t="s" s="2">
+        <v>906</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>906</v>
+      </c>
+      <c r="C266" s="2"/>
+      <c r="D266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E266" s="2"/>
+      <c r="F266" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G266" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K266" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L266" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M266" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N266" s="2"/>
+      <c r="O266" s="2"/>
+      <c r="P266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q266" s="2"/>
+      <c r="R266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF266" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG266" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH266" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN266" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO266" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP266" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="267" hidden="true">
+      <c r="A267" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="C267" s="2"/>
+      <c r="D267" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E267" s="2"/>
+      <c r="F267" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G267" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K267" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L267" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M267" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N267" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O267" s="2"/>
+      <c r="P267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q267" s="2"/>
+      <c r="R267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF267" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG267" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH267" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ267" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN267" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO267" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP267" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="268" hidden="true">
+      <c r="A268" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="C268" s="2"/>
+      <c r="D268" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="E268" s="2"/>
+      <c r="F268" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G268" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I268" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J268" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K268" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L268" t="s" s="2">
+        <v>910</v>
+      </c>
+      <c r="M268" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="N268" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O268" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="P268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q268" s="2"/>
+      <c r="R268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF268" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="AG268" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH268" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ268" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN268" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AO268" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP268" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="269" hidden="true">
+      <c r="A269" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="C269" s="2"/>
+      <c r="D269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E269" s="2"/>
+      <c r="F269" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G269" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K269" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L269" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="M269" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="N269" s="2"/>
+      <c r="O269" t="s" s="2">
+        <v>916</v>
+      </c>
+      <c r="P269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q269" s="2"/>
+      <c r="R269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X269" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y269" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="Z269" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="AA269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF269" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="AG269" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH269" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ269" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN269" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="AO269" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP269" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="270" hidden="true">
+      <c r="A270" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="C270" s="2"/>
+      <c r="D270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E270" s="2"/>
+      <c r="F270" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G270" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K270" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="L270" t="s" s="2">
+        <v>922</v>
+      </c>
+      <c r="M270" t="s" s="2">
+        <v>923</v>
+      </c>
+      <c r="N270" s="2"/>
+      <c r="O270" t="s" s="2">
+        <v>924</v>
+      </c>
+      <c r="P270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q270" s="2"/>
+      <c r="R270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF270" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="AG270" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH270" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ270" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM270" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="AN270" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="AO270" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP270" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="271" hidden="true">
+      <c r="A271" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="C271" s="2"/>
+      <c r="D271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E271" s="2"/>
+      <c r="F271" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G271" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K271" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="L271" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="M271" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N271" s="2"/>
+      <c r="O271" t="s" s="2">
+        <v>929</v>
+      </c>
+      <c r="P271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q271" s="2"/>
+      <c r="R271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF271" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="AG271" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH271" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI271" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AJ271" t="s" s="2">
+        <v>930</v>
+      </c>
+      <c r="AK271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL271" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM271" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AN271" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="AO271" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="AP271" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="272" hidden="true">
+      <c r="A272" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="C272" s="2"/>
+      <c r="D272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E272" s="2"/>
+      <c r="F272" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G272" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K272" t="s" s="2">
+        <v>932</v>
+      </c>
+      <c r="L272" t="s" s="2">
+        <v>933</v>
+      </c>
+      <c r="M272" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="N272" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="O272" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="P272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q272" s="2"/>
+      <c r="R272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF272" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="AG272" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH272" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI272" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AJ272" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL272" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM272" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="AN272" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="AO272" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="AP272" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="273" hidden="true">
+      <c r="A273" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="C273" s="2"/>
+      <c r="D273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E273" s="2"/>
+      <c r="F273" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G273" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H273" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K273" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="L273" t="s" s="2">
+        <v>937</v>
+      </c>
+      <c r="M273" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="N273" s="2"/>
+      <c r="O273" t="s" s="2">
+        <v>939</v>
+      </c>
+      <c r="P273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q273" s="2"/>
+      <c r="R273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF273" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="AG273" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH273" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ273" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN273" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP273" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP221">
+  <autoFilter ref="A1:AP273">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -29593,7 +36022,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI220">
+  <conditionalFormatting sqref="A2:AI272">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$221</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10387" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8441" uniqueCount="859">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2421,255 +2421,6 @@
   </si>
   <si>
     <t>EntiteJuridique.boiteLettreMSS</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.url</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.value[x]</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
-  &lt;code value="MSSANTE"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>typeBAL : Type de boîte aux lettres.
-Valeurs possibles : ORG | APP | PER | CAB</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible</t>
-  </si>
-  <si>
-    <t>responsible</t>
-  </si>
-  <si>
-    <t>responsable : Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service</t>
-  </si>
-  <si>
-    <t>service</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>telephone : Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté.</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization</t>
-  </si>
-  <si>
-    <t>digitization</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge</t>
-  </si>
-  <si>
-    <t>listeRouge</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.id</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.url</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>Boîte Aux Lettres (BAL) MSS</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>Organization.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -3253,20 +3004,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP273"/>
+  <dimension ref="A1:AP221"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="97.4375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.4375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="40.16796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="68.734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.03125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="34.4375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="125.07421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3275,28 +3026,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="108.3828125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="89.67578125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="92.91796875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="76.87890625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="39.41015625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.2578125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="218.1953125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="33.78515625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="37.0859375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="187.0625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27794,7 +27545,7 @@
         <v>775</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>723</v>
+        <v>775</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27805,10 +27556,10 @@
         <v>80</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>79</v>
@@ -27817,16 +27568,20 @@
         <v>79</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>105</v>
+        <v>776</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>106</v>
+        <v>777</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2"/>
+        <v>778</v>
+      </c>
+      <c r="N205" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="O205" t="s" s="2">
+        <v>780</v>
+      </c>
       <c r="P205" t="s" s="2">
         <v>79</v>
       </c>
@@ -27874,34 +27629,34 @@
         <v>79</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>108</v>
+        <v>775</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>79</v>
+        <v>781</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>79</v>
+        <v>782</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>79</v>
+        <v>783</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>79</v>
+        <v>784</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>109</v>
+        <v>785</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>79</v>
+        <v>786</v>
       </c>
       <c r="AP205" t="s" s="2">
         <v>79</v>
@@ -27909,10 +27664,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>724</v>
+        <v>787</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27920,10 +27675,10 @@
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>79</v>
@@ -27932,19 +27687,21 @@
         <v>79</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>112</v>
+        <v>788</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>202</v>
+        <v>789</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>203</v>
+        <v>790</v>
       </c>
       <c r="N206" s="2"/>
-      <c r="O206" s="2"/>
+      <c r="O206" t="s" s="2">
+        <v>791</v>
+      </c>
       <c r="P206" t="s" s="2">
         <v>79</v>
       </c>
@@ -27980,46 +27737,46 @@
         <v>79</v>
       </c>
       <c r="AB206" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC206" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE206" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>119</v>
+        <v>787</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>79</v>
+        <v>792</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>79</v>
+        <v>536</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>79</v>
+        <v>793</v>
       </c>
       <c r="AO206" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AP206" t="s" s="2">
         <v>79</v>
@@ -28027,20 +27784,18 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>777</v>
+        <v>794</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C207" t="s" s="2">
-        <v>726</v>
-      </c>
+        <v>794</v>
+      </c>
+      <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G207" t="s" s="2">
         <v>91</v>
@@ -28055,13 +27810,13 @@
         <v>79</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>727</v>
+        <v>105</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>728</v>
+        <v>106</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>729</v>
+        <v>107</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -28112,19 +27867,19 @@
         <v>79</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>79</v>
@@ -28136,7 +27891,7 @@
         <v>79</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>79</v>
@@ -28147,21 +27902,21 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>778</v>
+        <v>795</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>779</v>
+        <v>795</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H208" t="s" s="2">
         <v>79</v>
@@ -28173,15 +27928,17 @@
         <v>79</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N208" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>79</v>
@@ -28218,31 +27975,31 @@
         <v>79</v>
       </c>
       <c r="AB208" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC208" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD208" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE208" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI208" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>79</v>
@@ -28265,10 +28022,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28279,7 +28036,7 @@
         <v>80</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>79</v>
@@ -28288,18 +28045,20 @@
         <v>79</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>202</v>
+        <v>797</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N209" s="2"/>
+        <v>798</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>799</v>
+      </c>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>79</v>
@@ -28336,31 +28095,31 @@
         <v>79</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>119</v>
+        <v>800</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI209" t="s" s="2">
-        <v>79</v>
+        <v>801</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>79</v>
@@ -28372,7 +28131,7 @@
         <v>79</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>79</v>
@@ -28383,10 +28142,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>782</v>
+        <v>802</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28394,7 +28153,7 @@
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G210" t="s" s="2">
         <v>91</v>
@@ -28406,19 +28165,19 @@
         <v>79</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K210" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>224</v>
+        <v>803</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>225</v>
+        <v>804</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>226</v>
+        <v>805</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -28426,7 +28185,7 @@
       </c>
       <c r="Q210" s="2"/>
       <c r="R210" t="s" s="2">
-        <v>784</v>
+        <v>79</v>
       </c>
       <c r="S210" t="s" s="2">
         <v>79</v>
@@ -28444,13 +28203,11 @@
         <v>79</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y210" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Y210" s="2"/>
       <c r="Z210" t="s" s="2">
-        <v>79</v>
+        <v>554</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>79</v>
@@ -28468,10 +28225,10 @@
         <v>79</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>228</v>
+        <v>806</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>91</v>
@@ -28480,7 +28237,7 @@
         <v>79</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>79</v>
@@ -28503,10 +28260,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>785</v>
+        <v>807</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28526,18 +28283,20 @@
         <v>79</v>
       </c>
       <c r="J211" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>155</v>
+        <v>305</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>232</v>
+        <v>808</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N211" s="2"/>
+        <v>809</v>
+      </c>
+      <c r="N211" t="s" s="2">
+        <v>810</v>
+      </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>79</v>
@@ -28547,7 +28306,7 @@
         <v>79</v>
       </c>
       <c r="S211" t="s" s="2">
-        <v>787</v>
+        <v>79</v>
       </c>
       <c r="T211" t="s" s="2">
         <v>79</v>
@@ -28562,11 +28321,13 @@
         <v>79</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y211" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y211" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z211" t="s" s="2">
-        <v>788</v>
+        <v>79</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>79</v>
@@ -28584,7 +28345,7 @@
         <v>79</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>234</v>
+        <v>811</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -28608,7 +28369,7 @@
         <v>79</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>200</v>
+        <v>812</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>79</v>
@@ -28619,14 +28380,12 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>789</v>
+        <v>813</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C212" t="s" s="2">
-        <v>790</v>
-      </c>
+        <v>813</v>
+      </c>
+      <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
         <v>79</v>
       </c>
@@ -28644,18 +28403,20 @@
         <v>79</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>791</v>
+        <v>105</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N212" s="2"/>
+        <v>815</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>816</v>
+      </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>79</v>
@@ -28704,19 +28465,19 @@
         <v>79</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>119</v>
+        <v>817</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>79</v>
@@ -28728,7 +28489,7 @@
         <v>79</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>79</v>
@@ -28739,10 +28500,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>794</v>
+        <v>818</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>779</v>
+        <v>818</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28753,7 +28514,7 @@
         <v>80</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>79</v>
@@ -28765,16 +28526,20 @@
         <v>79</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>105</v>
+        <v>819</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>106</v>
+        <v>820</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N213" s="2"/>
-      <c r="O213" s="2"/>
+        <v>821</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="O213" t="s" s="2">
+        <v>823</v>
+      </c>
       <c r="P213" t="s" s="2">
         <v>79</v>
       </c>
@@ -28822,19 +28587,19 @@
         <v>79</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>108</v>
+        <v>818</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>79</v>
@@ -28846,7 +28611,7 @@
         <v>79</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>109</v>
+        <v>824</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>79</v>
@@ -28857,21 +28622,21 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>781</v>
+        <v>825</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>79</v>
@@ -28883,17 +28648,15 @@
         <v>79</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N214" s="2"/>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>79</v>
@@ -28930,31 +28693,31 @@
         <v>79</v>
       </c>
       <c r="AB214" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC214" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE214" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>79</v>
@@ -28977,23 +28740,21 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>797</v>
-      </c>
+        <v>826</v>
+      </c>
+      <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>79</v>
@@ -29008,12 +28769,14 @@
         <v>112</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>798</v>
+        <v>113</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N215" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>79</v>
@@ -29086,7 +28849,7 @@
         <v>79</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>79</v>
@@ -29097,42 +28860,46 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>799</v>
+        <v>827</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>800</v>
+        <v>827</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>79</v>
+        <v>828</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I216" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>106</v>
+        <v>829</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N216" s="2"/>
-      <c r="O216" s="2"/>
+        <v>830</v>
+      </c>
+      <c r="N216" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O216" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P216" t="s" s="2">
         <v>79</v>
       </c>
@@ -29180,19 +28947,19 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>108</v>
+        <v>831</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>79</v>
@@ -29204,7 +28971,7 @@
         <v>79</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>109</v>
+        <v>200</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>79</v>
@@ -29215,10 +28982,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>801</v>
+        <v>832</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>802</v>
+        <v>832</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29229,7 +28996,7 @@
         <v>80</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H217" t="s" s="2">
         <v>79</v>
@@ -29241,16 +29008,18 @@
         <v>79</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>112</v>
+        <v>339</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>202</v>
+        <v>833</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>203</v>
+        <v>834</v>
       </c>
       <c r="N217" s="2"/>
-      <c r="O217" s="2"/>
+      <c r="O217" t="s" s="2">
+        <v>835</v>
+      </c>
       <c r="P217" t="s" s="2">
         <v>79</v>
       </c>
@@ -29274,43 +29043,43 @@
         <v>79</v>
       </c>
       <c r="X217" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>79</v>
+        <v>836</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>79</v>
+        <v>837</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB217" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC217" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD217" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE217" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>119</v>
+        <v>832</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH217" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI217" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>79</v>
@@ -29322,7 +29091,7 @@
         <v>79</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>79</v>
+        <v>838</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>79</v>
@@ -29333,10 +29102,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>803</v>
+        <v>839</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>804</v>
+        <v>839</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29344,7 +29113,7 @@
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G218" t="s" s="2">
         <v>91</v>
@@ -29359,24 +29128,24 @@
         <v>79</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>138</v>
+        <v>840</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>224</v>
+        <v>841</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N218" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O218" s="2"/>
+        <v>842</v>
+      </c>
+      <c r="N218" s="2"/>
+      <c r="O218" t="s" s="2">
+        <v>843</v>
+      </c>
       <c r="P218" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q218" s="2"/>
       <c r="R218" t="s" s="2">
-        <v>797</v>
+        <v>79</v>
       </c>
       <c r="S218" t="s" s="2">
         <v>79</v>
@@ -29418,10 +29187,10 @@
         <v>79</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>228</v>
+        <v>839</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>91</v>
@@ -29430,7 +29199,7 @@
         <v>79</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK218" t="s" s="2">
         <v>79</v>
@@ -29439,10 +29208,10 @@
         <v>79</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>79</v>
+        <v>844</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>200</v>
+        <v>845</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>79</v>
@@ -29453,10 +29222,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>805</v>
+        <v>846</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>806</v>
+        <v>846</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29467,7 +29236,7 @@
         <v>80</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>79</v>
@@ -29479,16 +29248,18 @@
         <v>79</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>339</v>
+        <v>711</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>232</v>
+        <v>847</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>573</v>
+        <v>713</v>
       </c>
       <c r="N219" s="2"/>
-      <c r="O219" s="2"/>
+      <c r="O219" t="s" s="2">
+        <v>848</v>
+      </c>
       <c r="P219" t="s" s="2">
         <v>79</v>
       </c>
@@ -29512,11 +29283,13 @@
         <v>79</v>
       </c>
       <c r="X219" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="Y219" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y219" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z219" t="s" s="2">
-        <v>807</v>
+        <v>79</v>
       </c>
       <c r="AA219" t="s" s="2">
         <v>79</v>
@@ -29534,19 +29307,19 @@
         <v>79</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>234</v>
+        <v>846</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>103</v>
+        <v>849</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>79</v>
@@ -29555,13 +29328,13 @@
         <v>79</v>
       </c>
       <c r="AM219" t="s" s="2">
-        <v>79</v>
+        <v>720</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>200</v>
+        <v>721</v>
       </c>
       <c r="AO219" t="s" s="2">
-        <v>79</v>
+        <v>722</v>
       </c>
       <c r="AP219" t="s" s="2">
         <v>79</v>
@@ -29569,14 +29342,12 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>808</v>
+        <v>850</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C220" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>850</v>
+      </c>
+      <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
         <v>79</v>
       </c>
@@ -29597,16 +29368,20 @@
         <v>79</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>112</v>
+        <v>851</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>202</v>
+        <v>852</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N220" s="2"/>
-      <c r="O220" s="2"/>
+        <v>778</v>
+      </c>
+      <c r="N220" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="O220" t="s" s="2">
+        <v>853</v>
+      </c>
       <c r="P220" t="s" s="2">
         <v>79</v>
       </c>
@@ -29654,19 +29429,19 @@
         <v>79</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>119</v>
+        <v>850</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK220" t="s" s="2">
         <v>79</v>
@@ -29675,13 +29450,13 @@
         <v>79</v>
       </c>
       <c r="AM220" t="s" s="2">
-        <v>79</v>
+        <v>784</v>
       </c>
       <c r="AN220" t="s" s="2">
-        <v>79</v>
+        <v>785</v>
       </c>
       <c r="AO220" t="s" s="2">
-        <v>79</v>
+        <v>786</v>
       </c>
       <c r="AP220" t="s" s="2">
         <v>79</v>
@@ -29689,10 +29464,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>809</v>
+        <v>854</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>800</v>
+        <v>854</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29703,10 +29478,10 @@
         <v>80</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>79</v>
@@ -29715,16 +29490,18 @@
         <v>79</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>105</v>
+        <v>855</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>106</v>
+        <v>856</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>107</v>
+        <v>857</v>
       </c>
       <c r="N221" s="2"/>
-      <c r="O221" s="2"/>
+      <c r="O221" t="s" s="2">
+        <v>858</v>
+      </c>
       <c r="P221" t="s" s="2">
         <v>79</v>
       </c>
@@ -29772,19 +29549,19 @@
         <v>79</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>108</v>
+        <v>854</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI221" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>79</v>
@@ -29805,6214 +29582,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="222" hidden="true">
-      <c r="A222" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="B222" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="C222" s="2"/>
-      <c r="D222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E222" s="2"/>
-      <c r="F222" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G222" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K222" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L222" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M222" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N222" s="2"/>
-      <c r="O222" s="2"/>
-      <c r="P222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q222" s="2"/>
-      <c r="R222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB222" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC222" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE222" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF222" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG222" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH222" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ222" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO222" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP222" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="223" hidden="true">
-      <c r="A223" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="B223" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="C223" s="2"/>
-      <c r="D223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E223" s="2"/>
-      <c r="F223" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G223" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K223" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L223" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M223" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N223" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O223" s="2"/>
-      <c r="P223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q223" s="2"/>
-      <c r="R223" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="S223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF223" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG223" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH223" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN223" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP223" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="224" hidden="true">
-      <c r="A224" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="B224" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="C224" s="2"/>
-      <c r="D224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E224" s="2"/>
-      <c r="F224" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G224" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K224" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L224" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M224" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N224" s="2"/>
-      <c r="O224" s="2"/>
-      <c r="P224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q224" s="2"/>
-      <c r="R224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF224" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG224" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH224" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ224" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN224" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO224" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP224" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="225" hidden="true">
-      <c r="A225" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C225" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="D225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E225" s="2"/>
-      <c r="F225" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G225" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K225" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L225" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="M225" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N225" s="2"/>
-      <c r="O225" s="2"/>
-      <c r="P225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q225" s="2"/>
-      <c r="R225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF225" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG225" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH225" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ225" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO225" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP225" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="226" hidden="true">
-      <c r="A226" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="C226" s="2"/>
-      <c r="D226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E226" s="2"/>
-      <c r="F226" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G226" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K226" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L226" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N226" s="2"/>
-      <c r="O226" s="2"/>
-      <c r="P226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q226" s="2"/>
-      <c r="R226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF226" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG226" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH226" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN226" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO226" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP226" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="227" hidden="true">
-      <c r="A227" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="C227" s="2"/>
-      <c r="D227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E227" s="2"/>
-      <c r="F227" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G227" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K227" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L227" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M227" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N227" s="2"/>
-      <c r="O227" s="2"/>
-      <c r="P227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q227" s="2"/>
-      <c r="R227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB227" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC227" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE227" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF227" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG227" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH227" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ227" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO227" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP227" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="228" hidden="true">
-      <c r="A228" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="B228" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="C228" s="2"/>
-      <c r="D228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E228" s="2"/>
-      <c r="F228" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G228" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K228" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L228" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O228" s="2"/>
-      <c r="P228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q228" s="2"/>
-      <c r="R228" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="S228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF228" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG228" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH228" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN228" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO228" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP228" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="229" hidden="true">
-      <c r="A229" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="C229" s="2"/>
-      <c r="D229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E229" s="2"/>
-      <c r="F229" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G229" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K229" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L229" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N229" s="2"/>
-      <c r="O229" s="2"/>
-      <c r="P229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q229" s="2"/>
-      <c r="R229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF229" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG229" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH229" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ229" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN229" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO229" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP229" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="230" hidden="true">
-      <c r="A230" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C230" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="D230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E230" s="2"/>
-      <c r="F230" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G230" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K230" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L230" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M230" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N230" s="2"/>
-      <c r="O230" s="2"/>
-      <c r="P230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q230" s="2"/>
-      <c r="R230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF230" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG230" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH230" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ230" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO230" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP230" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="231" hidden="true">
-      <c r="A231" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="C231" s="2"/>
-      <c r="D231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E231" s="2"/>
-      <c r="F231" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G231" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K231" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L231" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M231" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N231" s="2"/>
-      <c r="O231" s="2"/>
-      <c r="P231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q231" s="2"/>
-      <c r="R231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF231" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG231" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH231" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN231" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP231" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="232" hidden="true">
-      <c r="A232" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="C232" s="2"/>
-      <c r="D232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E232" s="2"/>
-      <c r="F232" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G232" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K232" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L232" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N232" s="2"/>
-      <c r="O232" s="2"/>
-      <c r="P232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q232" s="2"/>
-      <c r="R232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB232" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC232" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE232" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF232" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG232" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH232" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ232" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO232" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP232" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="233" hidden="true">
-      <c r="A233" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="C233" s="2"/>
-      <c r="D233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E233" s="2"/>
-      <c r="F233" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G233" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K233" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L233" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O233" s="2"/>
-      <c r="P233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q233" s="2"/>
-      <c r="R233" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="S233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF233" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG233" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH233" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN233" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO233" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP233" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="234" hidden="true">
-      <c r="A234" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="C234" s="2"/>
-      <c r="D234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E234" s="2"/>
-      <c r="F234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G234" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K234" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L234" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N234" s="2"/>
-      <c r="O234" s="2"/>
-      <c r="P234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q234" s="2"/>
-      <c r="R234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF234" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH234" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ234" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN234" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO234" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP234" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="235" hidden="true">
-      <c r="A235" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C235" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="D235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E235" s="2"/>
-      <c r="F235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G235" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K235" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L235" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N235" s="2"/>
-      <c r="O235" s="2"/>
-      <c r="P235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q235" s="2"/>
-      <c r="R235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF235" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH235" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ235" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO235" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP235" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="236" hidden="true">
-      <c r="A236" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="C236" s="2"/>
-      <c r="D236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E236" s="2"/>
-      <c r="F236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G236" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K236" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L236" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N236" s="2"/>
-      <c r="O236" s="2"/>
-      <c r="P236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q236" s="2"/>
-      <c r="R236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF236" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH236" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN236" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO236" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP236" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="237" hidden="true">
-      <c r="A237" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="C237" s="2"/>
-      <c r="D237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E237" s="2"/>
-      <c r="F237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K237" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L237" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N237" s="2"/>
-      <c r="O237" s="2"/>
-      <c r="P237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q237" s="2"/>
-      <c r="R237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB237" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC237" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE237" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF237" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH237" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ237" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO237" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP237" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="238" hidden="true">
-      <c r="A238" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="B238" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="C238" s="2"/>
-      <c r="D238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E238" s="2"/>
-      <c r="F238" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G238" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K238" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L238" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M238" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N238" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O238" s="2"/>
-      <c r="P238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q238" s="2"/>
-      <c r="R238" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="S238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF238" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG238" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH238" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN238" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO238" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP238" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="239" hidden="true">
-      <c r="A239" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="B239" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="C239" s="2"/>
-      <c r="D239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E239" s="2"/>
-      <c r="F239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G239" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K239" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L239" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M239" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N239" s="2"/>
-      <c r="O239" s="2"/>
-      <c r="P239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q239" s="2"/>
-      <c r="R239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF239" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH239" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ239" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN239" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP239" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="240" hidden="true">
-      <c r="A240" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="B240" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C240" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="D240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E240" s="2"/>
-      <c r="F240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G240" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K240" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L240" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M240" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N240" s="2"/>
-      <c r="O240" s="2"/>
-      <c r="P240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q240" s="2"/>
-      <c r="R240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF240" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH240" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ240" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO240" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP240" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="241" hidden="true">
-      <c r="A241" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="C241" s="2"/>
-      <c r="D241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E241" s="2"/>
-      <c r="F241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G241" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K241" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L241" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N241" s="2"/>
-      <c r="O241" s="2"/>
-      <c r="P241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q241" s="2"/>
-      <c r="R241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF241" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH241" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN241" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP241" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="242" hidden="true">
-      <c r="A242" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="C242" s="2"/>
-      <c r="D242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E242" s="2"/>
-      <c r="F242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K242" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L242" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N242" s="2"/>
-      <c r="O242" s="2"/>
-      <c r="P242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q242" s="2"/>
-      <c r="R242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB242" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC242" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE242" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF242" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH242" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ242" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP242" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="243" hidden="true">
-      <c r="A243" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="C243" s="2"/>
-      <c r="D243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E243" s="2"/>
-      <c r="F243" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G243" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K243" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L243" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N243" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O243" s="2"/>
-      <c r="P243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q243" s="2"/>
-      <c r="R243" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="S243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF243" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG243" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH243" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN243" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP243" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="244" hidden="true">
-      <c r="A244" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="C244" s="2"/>
-      <c r="D244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E244" s="2"/>
-      <c r="F244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G244" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K244" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="L244" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M244" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N244" s="2"/>
-      <c r="O244" s="2"/>
-      <c r="P244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q244" s="2"/>
-      <c r="R244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF244" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH244" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ244" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN244" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP244" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="245" hidden="true">
-      <c r="A245" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C245" t="s" s="2">
-        <v>840</v>
-      </c>
-      <c r="D245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E245" s="2"/>
-      <c r="F245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G245" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K245" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L245" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M245" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N245" s="2"/>
-      <c r="O245" s="2"/>
-      <c r="P245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q245" s="2"/>
-      <c r="R245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF245" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH245" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ245" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP245" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="246" hidden="true">
-      <c r="A246" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="B246" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="C246" s="2"/>
-      <c r="D246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E246" s="2"/>
-      <c r="F246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G246" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K246" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L246" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M246" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N246" s="2"/>
-      <c r="O246" s="2"/>
-      <c r="P246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q246" s="2"/>
-      <c r="R246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF246" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH246" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN246" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP246" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="247" hidden="true">
-      <c r="A247" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="C247" s="2"/>
-      <c r="D247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E247" s="2"/>
-      <c r="F247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K247" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L247" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M247" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N247" s="2"/>
-      <c r="O247" s="2"/>
-      <c r="P247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q247" s="2"/>
-      <c r="R247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB247" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC247" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE247" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF247" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH247" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ247" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP247" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="248" hidden="true">
-      <c r="A248" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="C248" s="2"/>
-      <c r="D248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E248" s="2"/>
-      <c r="F248" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G248" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K248" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L248" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M248" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N248" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O248" s="2"/>
-      <c r="P248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q248" s="2"/>
-      <c r="R248" t="s" s="2">
-        <v>840</v>
-      </c>
-      <c r="S248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF248" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG248" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH248" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN248" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP248" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="249" hidden="true">
-      <c r="A249" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="C249" s="2"/>
-      <c r="D249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E249" s="2"/>
-      <c r="F249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G249" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K249" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="L249" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M249" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N249" s="2"/>
-      <c r="O249" s="2"/>
-      <c r="P249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q249" s="2"/>
-      <c r="R249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF249" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH249" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ249" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN249" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP249" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="250" hidden="true">
-      <c r="A250" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="C250" s="2"/>
-      <c r="D250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E250" s="2"/>
-      <c r="F250" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G250" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K250" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L250" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M250" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N250" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O250" s="2"/>
-      <c r="P250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q250" s="2"/>
-      <c r="R250" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="S250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF250" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG250" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH250" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN250" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP250" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="251" hidden="true">
-      <c r="A251" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="C251" s="2"/>
-      <c r="D251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E251" s="2"/>
-      <c r="F251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K251" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="L251" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M251" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N251" s="2"/>
-      <c r="O251" s="2"/>
-      <c r="P251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q251" s="2"/>
-      <c r="R251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF251" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH251" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ251" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN251" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP251" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="252" hidden="true">
-      <c r="A252" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C252" s="2"/>
-      <c r="D252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E252" s="2"/>
-      <c r="F252" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G252" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J252" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K252" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="L252" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="M252" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N252" s="2"/>
-      <c r="O252" s="2"/>
-      <c r="P252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q252" s="2"/>
-      <c r="R252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S252" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="T252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X252" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="Y252" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="Z252" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AA252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF252" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="AG252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH252" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI252" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="AJ252" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM252" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="AN252" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="AO252" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="AP252" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="253" hidden="true">
-      <c r="A253" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C253" s="2"/>
-      <c r="D253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E253" s="2"/>
-      <c r="F253" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G253" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H253" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J253" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K253" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L253" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="M253" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N253" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="O253" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="P253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q253" s="2"/>
-      <c r="R253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF253" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="AG253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH253" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ253" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM253" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="AN253" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="AO253" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AP253" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="254" hidden="true">
-      <c r="A254" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="C254" s="2"/>
-      <c r="D254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E254" s="2"/>
-      <c r="F254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G254" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I254" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J254" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K254" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="L254" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="M254" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="N254" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="O254" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="P254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q254" s="2"/>
-      <c r="R254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X254" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="Y254" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="Z254" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="AA254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF254" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="AG254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH254" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ254" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM254" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="AN254" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="AO254" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="AP254" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="255" hidden="true">
-      <c r="A255" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="C255" s="2"/>
-      <c r="D255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E255" s="2"/>
-      <c r="F255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G255" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J255" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K255" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="L255" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="M255" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="N255" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="O255" s="2"/>
-      <c r="P255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q255" s="2"/>
-      <c r="R255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF255" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="AG255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH255" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ255" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM255" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AN255" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP255" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="256" hidden="true">
-      <c r="A256" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="B256" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="C256" s="2"/>
-      <c r="D256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E256" s="2"/>
-      <c r="F256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G256" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J256" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K256" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L256" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="M256" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="N256" s="2"/>
-      <c r="O256" s="2"/>
-      <c r="P256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q256" s="2"/>
-      <c r="R256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF256" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="AG256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH256" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ256" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM256" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AN256" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="AO256" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AP256" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="257" hidden="true">
-      <c r="A257" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="B257" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="C257" s="2"/>
-      <c r="D257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E257" s="2"/>
-      <c r="F257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G257" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H257" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K257" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="L257" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="M257" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N257" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="O257" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="P257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q257" s="2"/>
-      <c r="R257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF257" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="AG257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH257" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI257" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AJ257" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="AK257" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="AL257" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="AM257" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="AN257" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="AO257" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="AP257" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="258" hidden="true">
-      <c r="A258" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="B258" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="C258" s="2"/>
-      <c r="D258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E258" s="2"/>
-      <c r="F258" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G258" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J258" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K258" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="L258" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="M258" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="N258" s="2"/>
-      <c r="O258" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="P258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q258" s="2"/>
-      <c r="R258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF258" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="AG258" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH258" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ258" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL258" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="AM258" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AN258" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="AO258" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AP258" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="259" hidden="true">
-      <c r="A259" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="B259" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="C259" s="2"/>
-      <c r="D259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E259" s="2"/>
-      <c r="F259" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G259" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K259" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L259" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M259" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N259" s="2"/>
-      <c r="O259" s="2"/>
-      <c r="P259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q259" s="2"/>
-      <c r="R259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF259" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG259" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH259" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN259" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO259" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP259" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="260" hidden="true">
-      <c r="A260" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="B260" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="C260" s="2"/>
-      <c r="D260" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E260" s="2"/>
-      <c r="F260" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G260" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K260" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L260" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M260" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N260" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O260" s="2"/>
-      <c r="P260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q260" s="2"/>
-      <c r="R260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB260" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC260" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE260" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF260" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG260" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH260" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ260" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN260" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO260" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP260" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="261" hidden="true">
-      <c r="A261" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="B261" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="C261" s="2"/>
-      <c r="D261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E261" s="2"/>
-      <c r="F261" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G261" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J261" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K261" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L261" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="M261" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="N261" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="O261" s="2"/>
-      <c r="P261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q261" s="2"/>
-      <c r="R261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF261" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="AG261" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH261" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI261" t="s" s="2">
-        <v>882</v>
-      </c>
-      <c r="AJ261" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN261" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO261" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP261" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="262" hidden="true">
-      <c r="A262" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="B262" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="C262" s="2"/>
-      <c r="D262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E262" s="2"/>
-      <c r="F262" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G262" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J262" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K262" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L262" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="M262" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="N262" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="O262" s="2"/>
-      <c r="P262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q262" s="2"/>
-      <c r="R262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X262" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y262" s="2"/>
-      <c r="Z262" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AA262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF262" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="AG262" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH262" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ262" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN262" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO262" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP262" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="263" hidden="true">
-      <c r="A263" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="B263" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="C263" s="2"/>
-      <c r="D263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E263" s="2"/>
-      <c r="F263" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G263" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J263" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K263" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L263" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="M263" t="s" s="2">
-        <v>890</v>
-      </c>
-      <c r="N263" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="O263" s="2"/>
-      <c r="P263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q263" s="2"/>
-      <c r="R263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF263" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="AG263" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH263" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ263" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN263" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="AO263" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP263" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="264" hidden="true">
-      <c r="A264" t="s" s="2">
-        <v>894</v>
-      </c>
-      <c r="B264" t="s" s="2">
-        <v>894</v>
-      </c>
-      <c r="C264" s="2"/>
-      <c r="D264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E264" s="2"/>
-      <c r="F264" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G264" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J264" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K264" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L264" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="M264" t="s" s="2">
-        <v>896</v>
-      </c>
-      <c r="N264" t="s" s="2">
-        <v>897</v>
-      </c>
-      <c r="O264" s="2"/>
-      <c r="P264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q264" s="2"/>
-      <c r="R264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF264" t="s" s="2">
-        <v>898</v>
-      </c>
-      <c r="AG264" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH264" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ264" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN264" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO264" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP264" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="265" hidden="true">
-      <c r="A265" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="B265" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="C265" s="2"/>
-      <c r="D265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E265" s="2"/>
-      <c r="F265" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G265" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K265" t="s" s="2">
-        <v>900</v>
-      </c>
-      <c r="L265" t="s" s="2">
-        <v>901</v>
-      </c>
-      <c r="M265" t="s" s="2">
-        <v>902</v>
-      </c>
-      <c r="N265" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="O265" t="s" s="2">
-        <v>904</v>
-      </c>
-      <c r="P265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q265" s="2"/>
-      <c r="R265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF265" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="AG265" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH265" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ265" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN265" t="s" s="2">
-        <v>905</v>
-      </c>
-      <c r="AO265" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP265" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="266" hidden="true">
-      <c r="A266" t="s" s="2">
-        <v>906</v>
-      </c>
-      <c r="B266" t="s" s="2">
-        <v>906</v>
-      </c>
-      <c r="C266" s="2"/>
-      <c r="D266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E266" s="2"/>
-      <c r="F266" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G266" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K266" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L266" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M266" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N266" s="2"/>
-      <c r="O266" s="2"/>
-      <c r="P266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q266" s="2"/>
-      <c r="R266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF266" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG266" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH266" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN266" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO266" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP266" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="267" hidden="true">
-      <c r="A267" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B267" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="C267" s="2"/>
-      <c r="D267" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E267" s="2"/>
-      <c r="F267" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G267" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K267" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L267" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M267" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N267" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O267" s="2"/>
-      <c r="P267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q267" s="2"/>
-      <c r="R267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF267" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG267" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH267" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ267" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN267" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP267" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="268" hidden="true">
-      <c r="A268" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="B268" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="C268" s="2"/>
-      <c r="D268" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="E268" s="2"/>
-      <c r="F268" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G268" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I268" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J268" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K268" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L268" t="s" s="2">
-        <v>910</v>
-      </c>
-      <c r="M268" t="s" s="2">
-        <v>911</v>
-      </c>
-      <c r="N268" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O268" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="P268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q268" s="2"/>
-      <c r="R268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF268" t="s" s="2">
-        <v>912</v>
-      </c>
-      <c r="AG268" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH268" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ268" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN268" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO268" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP268" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="269" hidden="true">
-      <c r="A269" t="s" s="2">
-        <v>913</v>
-      </c>
-      <c r="B269" t="s" s="2">
-        <v>913</v>
-      </c>
-      <c r="C269" s="2"/>
-      <c r="D269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E269" s="2"/>
-      <c r="F269" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G269" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K269" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="L269" t="s" s="2">
-        <v>914</v>
-      </c>
-      <c r="M269" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="N269" s="2"/>
-      <c r="O269" t="s" s="2">
-        <v>916</v>
-      </c>
-      <c r="P269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q269" s="2"/>
-      <c r="R269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X269" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y269" t="s" s="2">
-        <v>917</v>
-      </c>
-      <c r="Z269" t="s" s="2">
-        <v>918</v>
-      </c>
-      <c r="AA269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF269" t="s" s="2">
-        <v>913</v>
-      </c>
-      <c r="AG269" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH269" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ269" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN269" t="s" s="2">
-        <v>919</v>
-      </c>
-      <c r="AO269" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP269" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="270" hidden="true">
-      <c r="A270" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="B270" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="C270" s="2"/>
-      <c r="D270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E270" s="2"/>
-      <c r="F270" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G270" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K270" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="L270" t="s" s="2">
-        <v>922</v>
-      </c>
-      <c r="M270" t="s" s="2">
-        <v>923</v>
-      </c>
-      <c r="N270" s="2"/>
-      <c r="O270" t="s" s="2">
-        <v>924</v>
-      </c>
-      <c r="P270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q270" s="2"/>
-      <c r="R270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF270" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="AG270" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH270" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ270" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM270" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="AN270" t="s" s="2">
-        <v>926</v>
-      </c>
-      <c r="AO270" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP270" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="271" hidden="true">
-      <c r="A271" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="B271" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="C271" s="2"/>
-      <c r="D271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E271" s="2"/>
-      <c r="F271" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G271" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K271" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="L271" t="s" s="2">
-        <v>928</v>
-      </c>
-      <c r="M271" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="N271" s="2"/>
-      <c r="O271" t="s" s="2">
-        <v>929</v>
-      </c>
-      <c r="P271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q271" s="2"/>
-      <c r="R271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF271" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="AG271" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH271" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI271" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AJ271" t="s" s="2">
-        <v>930</v>
-      </c>
-      <c r="AK271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL271" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM271" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AN271" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AO271" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="AP271" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="272" hidden="true">
-      <c r="A272" t="s" s="2">
-        <v>931</v>
-      </c>
-      <c r="B272" t="s" s="2">
-        <v>931</v>
-      </c>
-      <c r="C272" s="2"/>
-      <c r="D272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E272" s="2"/>
-      <c r="F272" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G272" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K272" t="s" s="2">
-        <v>932</v>
-      </c>
-      <c r="L272" t="s" s="2">
-        <v>933</v>
-      </c>
-      <c r="M272" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N272" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="O272" t="s" s="2">
-        <v>934</v>
-      </c>
-      <c r="P272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q272" s="2"/>
-      <c r="R272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF272" t="s" s="2">
-        <v>931</v>
-      </c>
-      <c r="AG272" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH272" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI272" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AJ272" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL272" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM272" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="AN272" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="AO272" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="AP272" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="273" hidden="true">
-      <c r="A273" t="s" s="2">
-        <v>935</v>
-      </c>
-      <c r="B273" t="s" s="2">
-        <v>935</v>
-      </c>
-      <c r="C273" s="2"/>
-      <c r="D273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E273" s="2"/>
-      <c r="F273" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G273" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H273" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K273" t="s" s="2">
-        <v>936</v>
-      </c>
-      <c r="L273" t="s" s="2">
-        <v>937</v>
-      </c>
-      <c r="M273" t="s" s="2">
-        <v>938</v>
-      </c>
-      <c r="N273" s="2"/>
-      <c r="O273" t="s" s="2">
-        <v>939</v>
-      </c>
-      <c r="P273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q273" s="2"/>
-      <c r="R273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF273" t="s" s="2">
-        <v>935</v>
-      </c>
-      <c r="AG273" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH273" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ273" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN273" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AO273" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP273" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AP273">
+  <autoFilter ref="A1:AP221">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -36022,7 +29593,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI272">
+  <conditionalFormatting sqref="A2:AI220">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
